--- a/New folder/DB file folder/4 August -Expanded capacity calculation_DB.xlsx
+++ b/New folder/DB file folder/4 August -Expanded capacity calculation_DB.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitk\Desktop\ooffice\New folder\Winding_pending_vs_stock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ooffice KST\New folder\DB file folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1AD2B7-281F-45B1-A895-EC17052196B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="capacity" sheetId="2" r:id="rId1"/>
@@ -30,33 +29,22 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'New-Cycle time TUBE'!$D$1:$W$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Routing '!$A$1:$O$13</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>DELL</author>
   </authors>
   <commentList>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E7" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="329">
   <si>
     <t>Packing</t>
   </si>
@@ -1552,20 +1540,30 @@
   <si>
     <t>Y-cone winding- 6 inch BF</t>
   </si>
+  <si>
+    <t>COMFO 40 Regular</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1923,326 +1921,328 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="28" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="18" fontId="9" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="3" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="26" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="18" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="21" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="21" fontId="33" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2253,68 +2253,68 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="19" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2327,41 +2327,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="27" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="17" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="7" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="8">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 2 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 2 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Normal 4" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2 2" xfId="3"/>
+    <cellStyle name="Normal 2 3" xfId="5"/>
+    <cellStyle name="Normal 2 4" xfId="7"/>
+    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 4" xfId="4"/>
+    <cellStyle name="Normal 5" xfId="6"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2638,22 +2697,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M54"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
     <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -2683,7 +2742,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2695,7 +2754,7 @@
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2717,7 +2776,7 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>295</v>
@@ -2737,7 +2796,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2765,7 +2824,7 @@
         <v>167.43999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="4">
@@ -2785,7 +2844,7 @@
         <v>229.37985</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="4">
@@ -2803,7 +2862,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -2823,7 +2882,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="4" t="s">
@@ -2841,7 +2900,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="4">
@@ -2855,7 +2914,7 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
@@ -2873,7 +2932,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="4"/>
@@ -2885,7 +2944,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
@@ -2907,7 +2966,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13">
       <c r="A14" s="1"/>
       <c r="B14" s="111" t="s">
         <v>243</v>
@@ -2927,7 +2986,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2949,7 +3008,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13">
       <c r="A16" s="1"/>
       <c r="B16" s="111" t="s">
         <v>23</v>
@@ -2969,7 +3028,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13">
       <c r="A17" s="5" t="s">
         <v>24</v>
       </c>
@@ -2983,7 +3042,7 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13">
       <c r="A18" s="6" t="s">
         <v>25</v>
       </c>
@@ -3001,7 +3060,7 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13">
       <c r="A19" s="6" t="s">
         <v>26</v>
       </c>
@@ -3019,7 +3078,7 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13">
       <c r="A20" s="6" t="s">
         <v>27</v>
       </c>
@@ -3037,7 +3096,7 @@
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13">
       <c r="A21" s="6" t="s">
         <v>28</v>
       </c>
@@ -3055,7 +3114,7 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="4"/>
@@ -3068,7 +3127,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="3"/>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13">
       <c r="A23" s="8" t="s">
         <v>29</v>
       </c>
@@ -3083,7 +3142,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="3"/>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
         <v>30</v>
       </c>
@@ -3107,7 +3166,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="3"/>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13">
       <c r="A25" s="76" t="s">
         <v>247</v>
       </c>
@@ -3140,7 +3199,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
         <v>32</v>
       </c>
@@ -3173,7 +3232,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
         <v>34</v>
       </c>
@@ -3202,7 +3261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13">
       <c r="A28" s="6" t="s">
         <v>36</v>
       </c>
@@ -3226,7 +3285,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="3"/>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13">
       <c r="A29" s="6" t="s">
         <v>35</v>
       </c>
@@ -3250,7 +3309,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="3"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13">
       <c r="A30" s="6" t="s">
         <v>248</v>
       </c>
@@ -3274,7 +3333,7 @@
       <c r="J30" s="4"/>
       <c r="K30" s="3"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13">
       <c r="A31" s="6" t="s">
         <v>37</v>
       </c>
@@ -3295,7 +3354,7 @@
       <c r="J31" s="4"/>
       <c r="K31" s="3"/>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="4">
@@ -3312,7 +3371,7 @@
       <c r="J32" s="4"/>
       <c r="K32" s="3"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11">
       <c r="A33" s="6" t="s">
         <v>39</v>
       </c>
@@ -3333,7 +3392,7 @@
       <c r="J33" s="4"/>
       <c r="K33" s="3"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="4"/>
@@ -3346,7 +3405,7 @@
       <c r="J34" s="4"/>
       <c r="K34" s="3"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11">
       <c r="A35" s="7" t="s">
         <v>42</v>
       </c>
@@ -3367,7 +3426,7 @@
       <c r="J35" s="4"/>
       <c r="K35" s="3"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="4">
@@ -3388,7 +3447,7 @@
       <c r="J36" s="4"/>
       <c r="K36" s="3"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11">
       <c r="A37" s="7" t="s">
         <v>43</v>
       </c>
@@ -3409,7 +3468,7 @@
       <c r="J37" s="4"/>
       <c r="K37" s="3"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11">
       <c r="A38" s="7"/>
       <c r="B38" s="7" t="s">
         <v>41</v>
@@ -3432,7 +3491,7 @@
       <c r="J38" s="4"/>
       <c r="K38" s="3"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -3445,7 +3504,7 @@
       <c r="J39" s="4"/>
       <c r="K39" s="3"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11">
       <c r="A40" s="1" t="s">
         <v>45</v>
       </c>
@@ -3476,7 +3535,7 @@
       </c>
       <c r="K40" s="3"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11">
       <c r="A41" s="1"/>
       <c r="B41" s="1" t="s">
         <v>242</v>
@@ -3499,7 +3558,7 @@
       <c r="J41" s="4"/>
       <c r="K41" s="3"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="4"/>
@@ -3512,7 +3571,7 @@
       <c r="J42" s="4"/>
       <c r="K42" s="3"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="4"/>
@@ -3525,7 +3584,7 @@
       <c r="J43" s="4"/>
       <c r="K43" s="3"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>245</v>
       </c>
@@ -3558,7 +3617,7 @@
       </c>
       <c r="K44" s="3"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>246</v>
       </c>
@@ -3590,7 +3649,7 @@
       </c>
       <c r="K45" s="3"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -3614,7 +3673,7 @@
       </c>
       <c r="K46" s="3"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
@@ -3627,7 +3686,7 @@
       <c r="J47" s="4"/>
       <c r="K47" s="3"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11">
       <c r="A48" s="1" t="s">
         <v>327</v>
       </c>
@@ -3648,7 +3707,7 @@
       <c r="J48" s="4"/>
       <c r="K48" s="3"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>57</v>
       </c>
@@ -3669,7 +3728,7 @@
       <c r="J49" s="4"/>
       <c r="K49" s="3"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11">
       <c r="A50" s="1" t="s">
         <v>59</v>
       </c>
@@ -3690,7 +3749,7 @@
       <c r="J50" s="4"/>
       <c r="K50" s="3"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -3703,26 +3762,26 @@
       <c r="J51" s="4"/>
       <c r="K51" s="3"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11">
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11">
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11">
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H38" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -3730,34 +3789,33 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:V59"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:V60"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" style="9" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.88671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.85546875" style="9" customWidth="1"/>
     <col min="6" max="6" width="5" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="4.88671875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" style="9" customWidth="1"/>
     <col min="10" max="10" width="8" style="9" customWidth="1"/>
-    <col min="11" max="11" width="10.33203125" style="9"/>
-    <col min="12" max="12" width="9.6640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" style="9" customWidth="1"/>
+    <col min="11" max="11" width="10.28515625" style="9"/>
+    <col min="12" max="12" width="9.7109375" style="9" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" style="9" customWidth="1"/>
     <col min="15" max="15" width="9" style="9" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" style="9"/>
-    <col min="17" max="17" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.109375" style="9" customWidth="1"/>
-    <col min="19" max="19" width="7.33203125" style="9" customWidth="1"/>
-    <col min="20" max="16384" width="10.33203125" style="9"/>
+    <col min="16" max="16" width="10.28515625" style="9"/>
+    <col min="17" max="17" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.140625" style="9" customWidth="1"/>
+    <col min="19" max="19" width="7.28515625" style="9" customWidth="1"/>
+    <col min="20" max="16384" width="10.28515625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="55.5" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -3825,7 +3883,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -3893,7 +3951,7 @@
         <v>233.76623376623382</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="18" customHeight="1">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -3961,7 +4019,7 @@
         <v>1361.4406779661017</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="18" customHeight="1">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -4029,7 +4087,7 @@
         <v>274.7633341029786</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="29.25" customHeight="1">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -4093,7 +4151,7 @@
         <v>205.78741065252484</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="23.25" customHeight="1">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -4157,7 +4215,7 @@
         <v>281.58793510068551</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="27.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="27.75" customHeight="1">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -4217,7 +4275,7 @@
         <v>291.40359397765911</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="25.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="25.5" customHeight="1">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -4285,7 +4343,7 @@
         <v>597.76744186046528</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="22.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="22.5" customHeight="1">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -4353,7 +4411,7 @@
         <v>896.65116279069798</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="18" customHeight="1">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -4421,7 +4479,7 @@
         <v>323.07692307692315</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" ht="18" customHeight="1">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -4489,73 +4547,67 @@
         <v>323.07692307692315</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+    <row r="12" spans="1:22" ht="27" customHeight="1">
+      <c r="A12" s="150">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="152" t="s">
         <v>237</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="151">
         <v>60</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="151">
         <v>50</v>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="151">
         <v>2</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="151">
         <v>2211</v>
       </c>
-      <c r="G12" s="19" t="s">
+      <c r="G12" s="152" t="s">
         <v>236</v>
       </c>
-      <c r="H12" s="16">
-        <v>45490</v>
-      </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16" t="s">
+      <c r="H12" s="151">
+        <v>18600</v>
+      </c>
+      <c r="I12" s="151"/>
+      <c r="J12" s="151" t="s">
         <v>211</v>
       </c>
-      <c r="K12" s="19">
-        <v>500</v>
-      </c>
-      <c r="L12" s="34">
-        <f>H12*1.005/K12+3</f>
-        <v>94.434899999999999</v>
-      </c>
-      <c r="M12" s="34">
+      <c r="K12" s="152">
+        <v>600</v>
+      </c>
+      <c r="L12" s="153">
+        <v>34.154999999999994</v>
+      </c>
+      <c r="M12" s="153">
         <v>1</v>
       </c>
-      <c r="N12" s="34">
-        <f t="shared" si="1"/>
-        <v>0.63535832621202548</v>
-      </c>
-      <c r="O12" s="34">
-        <f>N12*21</f>
-        <v>13.342524850452534</v>
-      </c>
-      <c r="P12" s="25">
+      <c r="N12" s="153">
+        <v>1.7566974088713223</v>
+      </c>
+      <c r="O12" s="153">
+        <v>36.890645586297765</v>
+      </c>
+      <c r="P12" s="155">
         <v>0.85</v>
       </c>
-      <c r="Q12" s="66">
-        <f t="shared" si="0"/>
-        <v>11.341146122884654</v>
-      </c>
-      <c r="R12" s="66">
-        <f t="shared" si="2"/>
-        <v>111.09988235294118</v>
-      </c>
-      <c r="S12" s="20">
+      <c r="Q12" s="156">
+        <v>31.357048748353101</v>
+      </c>
+      <c r="R12" s="156">
+        <v>40.182352941176468</v>
+      </c>
+      <c r="S12" s="154">
         <v>10</v>
       </c>
-      <c r="T12" s="66">
-        <f t="shared" si="3"/>
-        <v>113.41146122884653</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T12" s="156">
+        <v>313.570487483531</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="18" customHeight="1">
       <c r="A13" s="15">
         <v>12</v>
       </c>
@@ -4623,7 +4675,7 @@
         <v>371.68141592920358</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="18" customHeight="1">
       <c r="A14" s="15">
         <v>13</v>
       </c>
@@ -4691,7 +4743,7 @@
         <v>296.57293497363798</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="18" customHeight="1">
       <c r="A15" s="15">
         <v>14</v>
       </c>
@@ -4759,7 +4811,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" ht="18" customHeight="1">
       <c r="A16" s="15">
         <v>15</v>
       </c>
@@ -4827,7 +4879,7 @@
         <v>1616.1151079136694</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="18" customHeight="1">
       <c r="A17" s="15">
         <v>16</v>
       </c>
@@ -4895,7 +4947,7 @@
         <v>409.09090909090912</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="18" customHeight="1">
       <c r="A18" s="15">
         <v>17</v>
       </c>
@@ -4963,7 +5015,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="18" customHeight="1">
       <c r="A19" s="15">
         <v>18</v>
       </c>
@@ -5031,7 +5083,7 @@
         <v>386.87837511082466</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="18" customHeight="1">
       <c r="A20" s="15">
         <v>19</v>
       </c>
@@ -5099,7 +5151,7 @@
         <v>675.86206896551732</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="18" customHeight="1">
       <c r="A21" s="15">
         <v>20</v>
       </c>
@@ -5167,7 +5219,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="18" customHeight="1">
       <c r="A22" s="15">
         <v>21</v>
       </c>
@@ -5231,7 +5283,7 @@
         <v>1432.2436849925707</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="18" customHeight="1">
       <c r="A23" s="15">
         <v>22</v>
       </c>
@@ -5295,7 +5347,7 @@
         <v>2594.6164199192472</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="18" customHeight="1">
       <c r="A24" s="15">
         <v>23</v>
       </c>
@@ -5359,7 +5411,7 @@
         <v>1432.2436849925707</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="18" customHeight="1">
       <c r="A25" s="15">
         <v>24</v>
       </c>
@@ -5423,7 +5475,7 @@
         <v>2594.6164199192472</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="18" customHeight="1">
       <c r="A26" s="15">
         <v>25</v>
       </c>
@@ -5487,7 +5539,7 @@
         <v>3165.5172413793107</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" ht="18" customHeight="1">
       <c r="A27" s="15">
         <v>26</v>
       </c>
@@ -5551,7 +5603,7 @@
         <v>2285.4771784232362</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" ht="18" customHeight="1">
       <c r="A28" s="15">
         <v>27</v>
       </c>
@@ -5615,7 +5667,7 @@
         <v>294.11764705882354</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:20" ht="18" customHeight="1">
       <c r="A29" s="15">
         <v>28</v>
       </c>
@@ -5683,7 +5735,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" ht="18" customHeight="1">
       <c r="A30" s="15">
         <v>29</v>
       </c>
@@ -5747,7 +5799,7 @@
         <v>2594.6164199192472</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:20" ht="18" customHeight="1">
       <c r="A31" s="15">
         <v>30</v>
       </c>
@@ -5811,7 +5863,7 @@
         <v>1432.2436849925707</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="18" customHeight="1">
       <c r="A32" s="15">
         <v>31</v>
       </c>
@@ -5879,7 +5931,7 @@
         <v>2421.64199192463</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:20" ht="25.9" customHeight="1">
       <c r="A33" s="15">
         <v>32</v>
       </c>
@@ -5947,7 +5999,7 @@
         <v>1336.760772659733</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="28.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:20" ht="28.9" customHeight="1">
       <c r="A34" s="15">
         <v>33</v>
       </c>
@@ -6015,7 +6067,7 @@
         <v>4269.7674418604656</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="37.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:20" ht="37.9" customHeight="1">
       <c r="A35" s="15">
         <v>34</v>
       </c>
@@ -6083,7 +6135,7 @@
         <v>831.26819126819134</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="25.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:20" ht="25.9" customHeight="1">
       <c r="A36" s="15">
         <v>35</v>
       </c>
@@ -6151,7 +6203,7 @@
         <v>2371.2177121771219</v>
       </c>
     </row>
-    <row r="37" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:20" ht="22.5">
       <c r="A37" s="15">
         <v>36</v>
       </c>
@@ -6219,7 +6271,7 @@
         <v>1361.4406779661017</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:20">
       <c r="A38" s="15">
         <v>37</v>
       </c>
@@ -6287,7 +6339,7 @@
         <v>1616.1151079136694</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:20">
       <c r="A39" s="15">
         <v>38</v>
       </c>
@@ -6355,7 +6407,7 @@
         <v>1616.1151079136694</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:20">
       <c r="A40" s="15">
         <v>39</v>
       </c>
@@ -6423,7 +6475,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:20">
       <c r="A41" s="15">
         <v>40</v>
       </c>
@@ -6491,7 +6543,7 @@
         <v>2371.2177121771219</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:20">
       <c r="A42" s="15">
         <v>41</v>
       </c>
@@ -6559,7 +6611,7 @@
         <v>1084.4956772334297</v>
       </c>
     </row>
-    <row r="43" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:20">
       <c r="A43" s="15">
         <v>42</v>
       </c>
@@ -6627,7 +6679,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:20">
       <c r="A44" s="15">
         <v>43</v>
       </c>
@@ -6695,7 +6747,7 @@
         <v>5147.663551401869</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:20">
       <c r="A45" s="15">
         <v>44</v>
       </c>
@@ -6763,7 +6815,7 @@
         <v>2371.2177121771219</v>
       </c>
     </row>
-    <row r="46" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:20">
       <c r="A46" s="15">
         <v>45</v>
       </c>
@@ -6828,7 +6880,7 @@
       </c>
       <c r="T46" s="33"/>
     </row>
-    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:20">
       <c r="A47" s="15">
         <v>46</v>
       </c>
@@ -6896,7 +6948,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="48" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:20">
       <c r="A48" s="15">
         <v>47</v>
       </c>
@@ -6964,7 +7016,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:20">
       <c r="A49" s="15">
         <v>48</v>
       </c>
@@ -7026,7 +7078,7 @@
         <v>2289.2768079800499</v>
       </c>
     </row>
-    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:20">
       <c r="A50" s="15">
         <v>49</v>
       </c>
@@ -7088,7 +7140,7 @@
         <v>2289.2768079800499</v>
       </c>
     </row>
-    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:20" ht="22.5">
       <c r="A51" s="15">
         <v>50</v>
       </c>
@@ -7156,7 +7208,7 @@
         <v>1432.2436849925707</v>
       </c>
     </row>
-    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:20">
       <c r="A52" s="15">
         <v>51</v>
       </c>
@@ -7224,7 +7276,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:20">
       <c r="A53" s="15">
         <v>52</v>
       </c>
@@ -7292,7 +7344,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:20">
       <c r="A54" s="15">
         <v>53</v>
       </c>
@@ -7360,7 +7412,7 @@
         <v>5147.663551401869</v>
       </c>
     </row>
-    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:20">
       <c r="A55" s="15">
         <v>54</v>
       </c>
@@ -7428,7 +7480,7 @@
         <v>1729.7442799461646</v>
       </c>
     </row>
-    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:20">
       <c r="A56" s="15">
         <v>55</v>
       </c>
@@ -7496,7 +7548,7 @@
         <v>3556.8265682656829</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:20" ht="22.5">
       <c r="A57" s="15">
         <v>56</v>
       </c>
@@ -7564,7 +7616,7 @@
         <v>248.3766233766234</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:20" ht="22.5">
       <c r="A58" s="15">
         <v>57</v>
       </c>
@@ -7632,7 +7684,7 @@
         <v>399.13043478260875</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="20.399999999999999" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:20" ht="22.5">
       <c r="A59" s="15">
         <v>58</v>
       </c>
@@ -7700,46 +7752,102 @@
         <v>220.44672537470115</v>
       </c>
     </row>
+    <row r="60" spans="1:20" ht="22.5">
+      <c r="A60" s="157">
+        <v>59</v>
+      </c>
+      <c r="B60" s="160" t="s">
+        <v>328</v>
+      </c>
+      <c r="C60" s="157">
+        <v>40</v>
+      </c>
+      <c r="D60" s="157">
+        <v>70</v>
+      </c>
+      <c r="E60" s="157">
+        <v>3</v>
+      </c>
+      <c r="F60" s="159">
+        <v>2327</v>
+      </c>
+      <c r="G60" s="158" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" s="159">
+        <v>1500</v>
+      </c>
+      <c r="I60" s="161" t="s">
+        <v>74</v>
+      </c>
+      <c r="J60" s="158" t="s">
+        <v>77</v>
+      </c>
+      <c r="K60" s="158">
+        <v>700</v>
+      </c>
+      <c r="L60" s="162">
+        <v>2.653571428571428</v>
+      </c>
+      <c r="M60" s="163">
+        <v>1</v>
+      </c>
+      <c r="N60" s="164">
+        <v>22.611036339165551</v>
+      </c>
+      <c r="O60" s="165">
+        <v>508.74831763122489</v>
+      </c>
+      <c r="P60" s="168">
+        <v>0.85</v>
+      </c>
+      <c r="Q60" s="166">
+        <v>432.43606998654116</v>
+      </c>
+      <c r="R60" s="166">
+        <v>3.1218487394957979</v>
+      </c>
+      <c r="S60" s="167">
+        <v>4</v>
+      </c>
+      <c r="T60" s="166">
+        <v>1729.7442799461646</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T59" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="2 in KS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:T59"/>
   <pageMargins left="0.51181102362204722" right="0.31496062992125984" top="0.15748031496062992" bottom="0.15748031496062992" header="0.11811023622047245" footer="0.11811023622047245"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:V25"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="120" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" style="132" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="132" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" style="132" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="132" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="132" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" style="132" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="132" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="132" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="132" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="132" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" style="132" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="120" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" style="132" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" style="132" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="132" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="132" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="132" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="132" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="132" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="132" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="132" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="132" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="132" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="132" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="132" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="132" customWidth="1"/>
-    <col min="16" max="20" width="10.33203125" style="120"/>
-    <col min="21" max="21" width="13.88671875" style="120" customWidth="1"/>
-    <col min="22" max="22" width="13.33203125" style="120" customWidth="1"/>
-    <col min="23" max="16384" width="10.33203125" style="120"/>
+    <col min="16" max="20" width="10.28515625" style="120"/>
+    <col min="21" max="21" width="13.85546875" style="120" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" style="120" customWidth="1"/>
+    <col min="23" max="16384" width="10.28515625" style="120"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="38.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="38.85" customHeight="1">
       <c r="A1" s="115" t="s">
         <v>238</v>
       </c>
@@ -7807,7 +7915,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="15" customHeight="1">
       <c r="A2" s="121">
         <v>1</v>
       </c>
@@ -7879,7 +7987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" ht="15" customHeight="1">
       <c r="A3" s="121">
         <v>2</v>
       </c>
@@ -7951,7 +8059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" ht="15" customHeight="1">
       <c r="A4" s="121">
         <v>3</v>
       </c>
@@ -8023,7 +8131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" ht="15" customHeight="1">
       <c r="A5" s="121">
         <v>4</v>
       </c>
@@ -8095,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" ht="15" customHeight="1">
       <c r="A6" s="121">
         <v>5</v>
       </c>
@@ -8163,7 +8271,7 @@
         <v>4812.1518987341778</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" ht="15" customHeight="1">
       <c r="A7" s="121">
         <v>6</v>
       </c>
@@ -8231,7 +8339,7 @@
         <v>4812.1518987341778</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="15" customHeight="1">
       <c r="A8" s="121">
         <v>7</v>
       </c>
@@ -8303,7 +8411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="15" customHeight="1">
       <c r="A9" s="121">
         <v>8</v>
       </c>
@@ -8375,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" ht="15" customHeight="1">
       <c r="A10" s="121">
         <v>9</v>
       </c>
@@ -8447,7 +8555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22">
       <c r="A11" s="121">
         <v>10</v>
       </c>
@@ -8519,7 +8627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22">
       <c r="A12" s="121">
         <v>11</v>
       </c>
@@ -8591,7 +8699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A13" s="121">
         <v>12</v>
       </c>
@@ -8663,7 +8771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A14" s="121">
         <v>13</v>
       </c>
@@ -8735,7 +8843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A15" s="121">
         <v>14</v>
       </c>
@@ -8807,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A16" s="121">
         <v>15</v>
       </c>
@@ -8879,7 +8987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="121">
         <v>16</v>
       </c>
@@ -8951,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A18" s="121">
         <v>17</v>
       </c>
@@ -9023,7 +9131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A19" s="121">
         <v>18</v>
       </c>
@@ -9095,7 +9203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" ht="16.149999999999999" customHeight="1">
       <c r="A20" s="121">
         <v>19</v>
       </c>
@@ -9167,7 +9275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" ht="18" customHeight="1">
       <c r="A21" s="121">
         <v>20</v>
       </c>
@@ -9239,7 +9347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" ht="27.75" customHeight="1">
       <c r="A22" s="121">
         <v>21</v>
       </c>
@@ -9311,7 +9419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" ht="35.25" customHeight="1">
       <c r="A23" s="121">
         <v>22</v>
       </c>
@@ -9383,7 +9491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" ht="27.6" customHeight="1">
       <c r="A24" s="121">
         <v>23</v>
       </c>
@@ -9455,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" ht="37.9" customHeight="1">
       <c r="A25" s="121">
         <v>24</v>
       </c>
@@ -9534,33 +9642,33 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W11"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" style="50" customWidth="1"/>
-    <col min="2" max="2" width="12.88671875" style="61" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="61" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.109375" style="61" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.5546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" style="61" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" style="61" customWidth="1"/>
-    <col min="9" max="9" width="5.109375" style="61" customWidth="1"/>
-    <col min="10" max="10" width="12.5546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.109375" style="61" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="61" customWidth="1"/>
-    <col min="13" max="13" width="7.6640625" style="61" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.88671875" style="61" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="50" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="61" customWidth="1"/>
+    <col min="3" max="3" width="5.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="61" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="61" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="61" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="61" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" style="61" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="61" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="61" customWidth="1"/>
+    <col min="12" max="12" width="8.5703125" style="61" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" style="61" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="61" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="61" customWidth="1"/>
-    <col min="16" max="20" width="10.33203125" style="50"/>
-    <col min="21" max="21" width="13.109375" style="50" customWidth="1"/>
-    <col min="22" max="22" width="11.5546875" style="50" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="17.6640625" style="50" customWidth="1"/>
-    <col min="24" max="16384" width="10.33203125" style="50"/>
+    <col min="16" max="20" width="10.28515625" style="50"/>
+    <col min="21" max="21" width="13.140625" style="50" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="50" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.7109375" style="50" customWidth="1"/>
+    <col min="24" max="16384" width="10.28515625" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="38.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="38.85" customHeight="1">
       <c r="A1" s="46" t="s">
         <v>62</v>
       </c>
@@ -9631,7 +9739,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="27.75" customHeight="1">
       <c r="A2" s="52">
         <v>1</v>
       </c>
@@ -9710,7 +9818,7 @@
         <v>200800</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" ht="29.25" customHeight="1">
       <c r="A3" s="52">
         <v>2</v>
       </c>
@@ -9789,7 +9897,7 @@
         <v>237209.58333333334</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" ht="36" customHeight="1">
       <c r="A4" s="52">
         <v>3</v>
       </c>
@@ -9868,7 +9976,7 @@
         <v>24191.590909090904</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="36" customHeight="1">
       <c r="A5" s="109">
         <v>4</v>
       </c>
@@ -9947,7 +10055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" ht="36" customHeight="1">
       <c r="A6" s="52">
         <v>5</v>
       </c>
@@ -10016,7 +10124,7 @@
       </c>
       <c r="V6" s="59"/>
     </row>
-    <row r="7" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="36" customHeight="1">
       <c r="A7" s="109">
         <v>6</v>
       </c>
@@ -10085,7 +10193,7 @@
       </c>
       <c r="V7" s="59"/>
     </row>
-    <row r="8" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="36" customHeight="1">
       <c r="A8" s="52">
         <v>7</v>
       </c>
@@ -10154,13 +10262,13 @@
       </c>
       <c r="V8" s="59"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23">
       <c r="W9" s="50">
         <f>SUM(W2:W4)</f>
         <v>462201.17424242425</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23">
       <c r="D10" s="61" t="s">
         <v>204</v>
       </c>
@@ -10169,7 +10277,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23">
       <c r="D11" s="61" t="s">
         <v>205</v>
       </c>
@@ -10179,41 +10287,41 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:W11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="D1:W11"/>
   <pageMargins left="0.51181102362204722" right="0.11811023622047245" top="0.15748031496062992" bottom="0.15748031496062992" header="0.11811023622047245" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:X18"/>
-  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" style="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" style="9" customWidth="1"/>
     <col min="3" max="3" width="4" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.44140625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="10.33203125" style="9"/>
-    <col min="17" max="18" width="12.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="10.33203125" style="9"/>
-    <col min="21" max="21" width="8.33203125" style="9" customWidth="1"/>
-    <col min="22" max="22" width="11.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="10.33203125" style="9"/>
+    <col min="7" max="7" width="9.28515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.42578125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="6.7109375" style="9" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" style="9" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="9" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="9.28515625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="9" customWidth="1"/>
+    <col min="16" max="16" width="10.28515625" style="9"/>
+    <col min="17" max="18" width="12.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.28515625" style="9"/>
+    <col min="21" max="21" width="8.28515625" style="9" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="10.28515625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="38.85" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="38.85" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>62</v>
       </c>
@@ -10281,7 +10389,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="2" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" ht="16.5" customHeight="1">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -10356,7 +10464,7 @@
         <v>59.796258992805761</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" ht="18" customHeight="1">
       <c r="A3" s="15">
         <v>2</v>
       </c>
@@ -10430,7 +10538,7 @@
         <v>193.76</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" ht="25.5" customHeight="1">
       <c r="A4" s="15">
         <v>3</v>
       </c>
@@ -10504,7 +10612,7 @@
         <v>551.17999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" ht="33.75" customHeight="1">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -10578,7 +10686,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" ht="24.75" customHeight="1">
       <c r="A6" s="15">
         <v>5</v>
       </c>
@@ -10652,7 +10760,7 @@
         <v>242.49</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24">
       <c r="A7" s="15">
         <v>6</v>
       </c>
@@ -10726,7 +10834,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24">
       <c r="A8" s="15">
         <v>7</v>
       </c>
@@ -10800,7 +10908,7 @@
         <v>265.024</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" ht="30.75" customHeight="1">
       <c r="A9" s="15">
         <v>8</v>
       </c>
@@ -10875,7 +10983,7 @@
         <v>475.4066985645934</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" ht="29.25" customHeight="1">
       <c r="A10" s="15">
         <v>9</v>
       </c>
@@ -10950,7 +11058,7 @@
         <v>238.13247011952188</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" ht="37.5" customHeight="1">
       <c r="A11" s="15">
         <v>10</v>
       </c>
@@ -11025,7 +11133,7 @@
         <v>52.026283367556466</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" ht="37.5" customHeight="1">
       <c r="A12" s="15">
         <v>11</v>
       </c>
@@ -11100,7 +11208,7 @@
         <v>63.475099348947325</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24">
       <c r="R13" s="77" t="s">
         <v>255</v>
       </c>
@@ -11113,7 +11221,7 @@
       <c r="W13" s="77"/>
       <c r="X13" s="77"/>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24">
       <c r="P14" s="79" t="s">
         <v>251</v>
       </c>
@@ -11135,7 +11243,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24">
       <c r="P15" s="82" t="s">
         <v>252</v>
       </c>
@@ -11157,7 +11265,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24">
       <c r="P16" s="82" t="s">
         <v>253</v>
       </c>
@@ -11182,32 +11290,32 @@
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="10:10">
       <c r="J18" s="135"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V16" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:V16"/>
   <pageMargins left="0.51181102362204722" right="0.31496062992125984" top="0.15748031496062992" bottom="0.15748031496062992" header="0.11811023622047245" footer="0.11811023622047245"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" customWidth="1"/>
     <col min="8" max="8" width="4" customWidth="1"/>
-    <col min="9" max="9" width="30.109375" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
+    <col min="9" max="9" width="30.140625" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="48.75" customHeight="1">
       <c r="L1" s="143" t="s">
         <v>306</v>
       </c>
@@ -11215,7 +11323,7 @@
       <c r="N1" s="143"/>
       <c r="O1" s="143"/>
     </row>
-    <row r="2" spans="1:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" ht="31.5" customHeight="1">
       <c r="A2" s="142" t="s">
         <v>299</v>
       </c>
@@ -11242,7 +11350,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
@@ -11280,7 +11388,7 @@
         <v>25.62</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>251</v>
       </c>
@@ -11318,7 +11426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>252</v>
       </c>
@@ -11358,7 +11466,7 @@
         <v>7.3199999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>253</v>
       </c>
@@ -11398,7 +11506,7 @@
         <v>10.979999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15">
       <c r="A7" s="139" t="s">
         <v>318</v>
       </c>
@@ -11433,7 +11541,7 @@
         <v>12.2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15">
       <c r="I8" s="1" t="s">
         <v>256</v>
       </c>
@@ -11457,7 +11565,7 @@
         <v>7.3199999999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="18.75">
       <c r="A9" s="134" t="s">
         <v>300</v>
       </c>
@@ -11491,7 +11599,7 @@
         <v>7.3199999999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15">
       <c r="C10" s="102"/>
       <c r="I10" s="1" t="s">
         <v>315</v>
@@ -11514,7 +11622,7 @@
         <v>26.840000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="18.75">
       <c r="A11" s="142" t="s">
         <v>302</v>
       </c>
@@ -11544,7 +11652,7 @@
         <v>21.959999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
@@ -11578,7 +11686,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>251</v>
       </c>
@@ -11615,7 +11723,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>252</v>
       </c>
@@ -11652,7 +11760,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>253</v>
       </c>
@@ -11685,7 +11793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15">
       <c r="E16">
         <f>E15*450</f>
         <v>1164600</v>
@@ -11712,19 +11820,19 @@
         <v>170.25999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6">
       <c r="E17">
         <f>E16*25</f>
         <v>29115000</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6">
       <c r="E18">
         <f>75000*450</f>
         <v>33750000</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="18.75">
       <c r="A20" s="136" t="s">
         <v>305</v>
       </c>
@@ -11750,27 +11858,27 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H46"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
+    <col min="1" max="1" width="52.140625" customWidth="1"/>
     <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="102"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="102"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:8" ht="15.75">
+      <c r="A1" s="144" t="s">
         <v>258</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="144"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.25">
       <c r="A2" s="84" t="s">
         <v>259</v>
       </c>
@@ -11780,26 +11888,26 @@
       <c r="E2" s="85"/>
       <c r="F2" s="86"/>
     </row>
-    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="A3" s="144" t="s">
+    <row r="3" spans="1:8" ht="15.75">
+      <c r="A3" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="C3" s="146" t="s">
+      <c r="C3" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="D3" s="147"/>
-      <c r="E3" s="146" t="s">
+      <c r="D3" s="148"/>
+      <c r="E3" s="147" t="s">
         <v>263</v>
       </c>
-      <c r="F3" s="147"/>
+      <c r="F3" s="148"/>
       <c r="H3" s="101"/>
     </row>
-    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="A4" s="145"/>
-      <c r="B4" s="145"/>
+    <row r="4" spans="1:8" ht="15.75">
+      <c r="A4" s="146"/>
+      <c r="B4" s="146"/>
       <c r="C4" s="87" t="s">
         <v>264</v>
       </c>
@@ -11813,7 +11921,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="18">
       <c r="A5" s="89" t="s">
         <v>267</v>
       </c>
@@ -11833,7 +11941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="18">
       <c r="A6" s="89" t="s">
         <v>269</v>
       </c>
@@ -11853,7 +11961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="18">
       <c r="A7" s="92" t="s">
         <v>270</v>
       </c>
@@ -11873,7 +11981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18">
       <c r="A8" s="89" t="s">
         <v>271</v>
       </c>
@@ -11893,7 +12001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18">
       <c r="A9" s="93" t="s">
         <v>272</v>
       </c>
@@ -11919,7 +12027,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="15.75">
       <c r="A10" s="96"/>
       <c r="B10" s="96"/>
       <c r="C10" s="96"/>
@@ -11928,7 +12036,7 @@
       <c r="F10" s="96"/>
       <c r="G10" s="83"/>
     </row>
-    <row r="11" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="20.25">
       <c r="A11" s="84" t="s">
         <v>273</v>
       </c>
@@ -11939,26 +12047,26 @@
       <c r="F11" s="85"/>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="144" t="s">
+    <row r="12" spans="1:8" ht="15.75">
+      <c r="A12" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="C12" s="146" t="s">
+      <c r="C12" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="D12" s="147"/>
-      <c r="E12" s="146" t="s">
+      <c r="D12" s="148"/>
+      <c r="E12" s="147" t="s">
         <v>263</v>
       </c>
-      <c r="F12" s="148"/>
+      <c r="F12" s="149"/>
       <c r="G12" s="83"/>
     </row>
-    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.3">
-      <c r="A13" s="145"/>
-      <c r="B13" s="145"/>
+    <row r="13" spans="1:8" ht="15.75">
+      <c r="A13" s="146"/>
+      <c r="B13" s="146"/>
       <c r="C13" s="87" t="s">
         <v>264</v>
       </c>
@@ -11973,7 +12081,7 @@
       </c>
       <c r="G13" s="83"/>
     </row>
-    <row r="14" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18">
       <c r="A14" s="89" t="s">
         <v>274</v>
       </c>
@@ -11993,7 +12101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18">
       <c r="A15" s="89" t="s">
         <v>275</v>
       </c>
@@ -12013,7 +12121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="18">
       <c r="A16" s="89" t="s">
         <v>276</v>
       </c>
@@ -12033,7 +12141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="18">
       <c r="A17" s="89" t="s">
         <v>277</v>
       </c>
@@ -12053,7 +12161,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="18">
       <c r="A18" s="89" t="s">
         <v>278</v>
       </c>
@@ -12073,7 +12181,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="18">
       <c r="A19" s="89" t="s">
         <v>279</v>
       </c>
@@ -12093,7 +12201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="18">
       <c r="A20" s="89" t="s">
         <v>280</v>
       </c>
@@ -12113,7 +12221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="18">
       <c r="A21" s="89" t="s">
         <v>281</v>
       </c>
@@ -12133,7 +12241,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="18">
       <c r="A22" s="89" t="s">
         <v>283</v>
       </c>
@@ -12153,7 +12261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="18">
       <c r="A23" s="93" t="s">
         <v>272</v>
       </c>
@@ -12179,7 +12287,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="86"/>
       <c r="B24" s="86"/>
       <c r="C24" s="86"/>
@@ -12191,7 +12299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="20.25">
       <c r="A25" s="84" t="s">
         <v>284</v>
       </c>
@@ -12205,26 +12313,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A26" s="144" t="s">
+    <row r="26" spans="1:7" ht="15.75">
+      <c r="A26" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="C26" s="146" t="s">
+      <c r="C26" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="D26" s="147"/>
-      <c r="E26" s="146" t="s">
+      <c r="D26" s="148"/>
+      <c r="E26" s="147" t="s">
         <v>263</v>
       </c>
-      <c r="F26" s="148"/>
+      <c r="F26" s="149"/>
       <c r="G26" s="83"/>
     </row>
-    <row r="27" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A27" s="145"/>
-      <c r="B27" s="145"/>
+    <row r="27" spans="1:7" ht="15.75">
+      <c r="A27" s="146"/>
+      <c r="B27" s="146"/>
       <c r="C27" s="87" t="s">
         <v>264</v>
       </c>
@@ -12239,7 +12347,7 @@
       </c>
       <c r="G27" s="83"/>
     </row>
-    <row r="28" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="18">
       <c r="A28" s="99" t="s">
         <v>285</v>
       </c>
@@ -12259,7 +12367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="18">
       <c r="A29" s="89" t="s">
         <v>281</v>
       </c>
@@ -12279,7 +12387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="18">
       <c r="A30" s="93" t="s">
         <v>272</v>
       </c>
@@ -12305,7 +12413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="20.25">
       <c r="A31" s="84"/>
       <c r="B31" s="84"/>
       <c r="C31" s="84"/>
@@ -12317,26 +12425,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A32" s="144" t="s">
+    <row r="32" spans="1:7" ht="15.75">
+      <c r="A32" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="B32" s="144" t="s">
+      <c r="B32" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="C32" s="146" t="s">
+      <c r="C32" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="D32" s="147"/>
-      <c r="E32" s="146" t="s">
+      <c r="D32" s="148"/>
+      <c r="E32" s="147" t="s">
         <v>263</v>
       </c>
-      <c r="F32" s="148"/>
+      <c r="F32" s="149"/>
       <c r="G32" s="83"/>
     </row>
-    <row r="33" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A33" s="145"/>
-      <c r="B33" s="145"/>
+    <row r="33" spans="1:7" ht="15.75">
+      <c r="A33" s="146"/>
+      <c r="B33" s="146"/>
       <c r="C33" s="87" t="s">
         <v>264</v>
       </c>
@@ -12351,7 +12459,7 @@
       </c>
       <c r="G33" s="83"/>
     </row>
-    <row r="34" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="18">
       <c r="A34" s="89" t="s">
         <v>286</v>
       </c>
@@ -12371,7 +12479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="18">
       <c r="A35" s="89" t="s">
         <v>287</v>
       </c>
@@ -12391,7 +12499,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="18">
       <c r="A36" s="89" t="s">
         <v>288</v>
       </c>
@@ -12411,7 +12519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="18">
       <c r="A37" s="89" t="s">
         <v>289</v>
       </c>
@@ -12431,7 +12539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="18">
       <c r="A38" s="89" t="s">
         <v>290</v>
       </c>
@@ -12451,7 +12559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="18">
       <c r="A39" s="93" t="s">
         <v>272</v>
       </c>
@@ -12477,7 +12585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="20.399999999999999" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="20.25">
       <c r="A40" s="84"/>
       <c r="B40" s="84"/>
       <c r="C40" s="84"/>
@@ -12486,26 +12594,26 @@
       <c r="F40" s="85"/>
       <c r="G40" s="83"/>
     </row>
-    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A41" s="144" t="s">
+    <row r="41" spans="1:7" ht="15.75">
+      <c r="A41" s="145" t="s">
         <v>260</v>
       </c>
-      <c r="B41" s="144" t="s">
+      <c r="B41" s="145" t="s">
         <v>261</v>
       </c>
-      <c r="C41" s="146" t="s">
+      <c r="C41" s="147" t="s">
         <v>262</v>
       </c>
-      <c r="D41" s="147"/>
-      <c r="E41" s="146" t="s">
+      <c r="D41" s="148"/>
+      <c r="E41" s="147" t="s">
         <v>263</v>
       </c>
-      <c r="F41" s="148"/>
+      <c r="F41" s="149"/>
       <c r="G41" s="83"/>
     </row>
-    <row r="42" spans="1:7" ht="15" x14ac:dyDescent="0.3">
-      <c r="A42" s="145"/>
-      <c r="B42" s="145"/>
+    <row r="42" spans="1:7" ht="15.75">
+      <c r="A42" s="146"/>
+      <c r="B42" s="146"/>
       <c r="C42" s="87" t="s">
         <v>264</v>
       </c>
@@ -12520,7 +12628,7 @@
       </c>
       <c r="G42" s="83"/>
     </row>
-    <row r="43" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="18">
       <c r="A43" s="98" t="s">
         <v>291</v>
       </c>
@@ -12540,7 +12648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="18">
       <c r="A44" s="98" t="s">
         <v>292</v>
       </c>
@@ -12560,7 +12668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="18">
       <c r="A45" s="93" t="s">
         <v>272</v>
       </c>
@@ -12580,7 +12688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7">
       <c r="A46" s="103" t="s">
         <v>293</v>
       </c>
@@ -12600,11 +12708,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="A26:A27"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="C26:D26"/>
@@ -12613,14 +12724,11 @@
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
@@ -12628,29 +12736,29 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L15"/>
-  <sheetFormatPr defaultColWidth="3.88671875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="3.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="21.88671875" style="31" customWidth="1"/>
-    <col min="2" max="2" width="11.33203125" style="31" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" style="31" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="31" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="31" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" style="31" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.5546875" style="31" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" style="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="31" customWidth="1"/>
     <col min="8" max="8" width="7" style="31" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" style="31" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="31" customWidth="1"/>
-    <col min="11" max="11" width="7.88671875" style="31" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="31" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="31" customWidth="1"/>
+    <col min="11" max="11" width="7.85546875" style="31" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="48" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" style="31" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.44140625" style="31" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5546875" style="31" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="3.88671875" style="31"/>
+    <col min="13" max="13" width="14.7109375" style="31" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.42578125" style="31" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5703125" style="31" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="3.85546875" style="31"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="28" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="28" customFormat="1" ht="39.75" customHeight="1">
       <c r="A1" s="26" t="s">
         <v>150</v>
       </c>
@@ -12685,7 +12793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12">
       <c r="A2" s="29" t="s">
         <v>169</v>
       </c>
@@ -12719,7 +12827,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" s="29" t="s">
         <v>158</v>
       </c>
@@ -12753,7 +12861,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" s="29" t="s">
         <v>158</v>
       </c>
@@ -12787,7 +12895,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" s="29" t="s">
         <v>158</v>
       </c>
@@ -12821,7 +12929,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" s="29" t="s">
         <v>98</v>
       </c>
@@ -12855,7 +12963,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" s="29" t="s">
         <v>161</v>
       </c>
@@ -12891,7 +12999,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" s="29">
         <v>4007</v>
       </c>
@@ -12915,7 +13023,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" s="29">
         <v>5009</v>
       </c>
@@ -12945,7 +13053,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" s="29" t="s">
         <v>167</v>
       </c>
@@ -12973,7 +13081,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" s="29" t="s">
         <v>168</v>
       </c>
@@ -12999,7 +13107,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" s="29">
         <v>5096</v>
       </c>
@@ -13027,7 +13135,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" s="29">
         <v>5708</v>
       </c>
@@ -13051,7 +13159,7 @@
       </c>
       <c r="L13" s="30"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12">
       <c r="A14" s="29">
         <v>5147</v>
       </c>
@@ -13081,7 +13189,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12">
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -13096,7 +13204,7 @@
       <c r="L15" s="30"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O13" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:O13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
